--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,96 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Пятигорск</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46289.70020833334</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SMT-в00011031910</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Администрация Пятигорск</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Необходимы щипцы для продукции СП ММ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Пятигорск</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46289.70180555555</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SMT-в00011031923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Администрация Пятигорск</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Необходимо закупить два люксметра для инженерной службы</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Пятигорск</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46289.70273148148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SMT-в00011031944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Администрация Пятигорск</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Необходима закупка совков для сыпучей продукции в колличестве 7 шт.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,40 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Необходима закупка совков для сыпучей продукции в колличестве 7 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Владикавказ</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SMT-в00011060302</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Инженерный отдел Владикавказ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SVET.PAP Возмещение ПАП в рамках договоров «субаренда доходная». Сентябрь 2026. Сотрудникам ИС необходимо: предоставить сведения о потреблении коммунальных услуг арендаторами помещений. 
+Заполнить показания учета энергоресурсов согласно прилагаемых шаблонов за отчетный период не позднее 17:00 25.09.2026 г.
+Требуется показания по каждому КА/ресурсу согласно перечня.
+Закрыть задачу в ТОиР с вложением заполненного шаблона и статусом «Решен».
+Если необходимые документы  направлены  в адрес Учет доходов ОЦО, прошу указать данную информацию  в комментарии, при закрытии заявки.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,40 +570,6 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Необходима закупка совков для сыпучей продукции в колличестве 7 шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Владикавказ</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SMT-в00011060302</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Инженерный отдел Владикавказ</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SVET.PAP Возмещение ПАП в рамках договоров «субаренда доходная». Сентябрь 2026. Сотрудникам ИС необходимо: предоставить сведения о потреблении коммунальных услуг арендаторами помещений. 
-Заполнить показания учета энергоресурсов согласно прилагаемых шаблонов за отчетный период не позднее 17:00 25.09.2026 г.
-Требуется показания по каждому КА/ресурсу согласно перечня.
-Закрыть задачу в ТОиР с вложением заполненного шаблона и статусом «Решен».
-Если необходимые документы  направлены  в адрес Учет доходов ОЦО, прошу указать данную информацию  в комментарии, при закрытии заявки.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,96 +480,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Пятигорск</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46289.70020833334</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SMT-в00011031910</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Администрация Пятигорск</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Необходимы щипцы для продукции СП ММ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Пятигорск</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46289.70180555555</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SMT-в00011031923</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Администрация Пятигорск</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Необходимо закупить два люксметра для инженерной службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Пятигорск</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46289.70273148148</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SMT-в00011031944</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Администрация Пятигорск</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Необходима закупка совков для сыпучей продукции в колличестве 7 шт.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,39 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46306.59444444445</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SMT-в00011245542</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Администрация Пенза</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Офис Пензенского филиала АО Тандер.
+1. В кабинете №7 (ОИТ) необходимо выполнить герметизацию примыканий окон к стенам. Промерзание в местах примыкания в ОЗП.
+2. В кабинете № 13 на радиатор смонтировать боковой автоматический воздухоотводчик.
+3. В кабинете ДФ МК смонтировать на радиатор боковой автоматический воздухоотводчик.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,52 @@
 1. В кабинете №7 (ОИТ) необходимо выполнить герметизацию примыканий окон к стенам. Промерзание в местах примыкания в ОЗП.
 2. В кабинете № 13 на радиатор смонтировать боковой автоматический воздухоотводчик.
 3. В кабинете ДФ МК смонтировать на радиатор боковой автоматический воздухоотводчик.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Владикавказ</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SMT-в00011341893</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Инженерный отдел Владикавказ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ежемесячное списание фреона_сентябрь_2026 Добрый день!
+Коллеги, ввиду наличия системной проблемы со списанием фреона с октября 2025 года на ежемесячной основе будет выполняться постановка задачи по списанию на все филиалы и РЦ.
+Срок выполнения задачи с 10 по 20 число каждого месяца. Централизованная поставка фреона на филиалы и РЦ будет учитывать текущие остатки по БУ, ввиду чего фактические остатки должны соответствовать остаткам БУ.
+Для выполнения задачи всем филиалам и РЦ требуется:
+1.  Выполнить списание фреона за последний отчётный период (месяц). Объем списания рассчитывается исходя из норматива расхода:
+•   ММ – 0,058 баллонов в месяц;
+•   БФ – 1,7 баллонов в месяц;
+•   РЦ – 10 баллонов в месяц.
+2.  При закрытии задачи в комментариях указать номер заявки в СЭД на списание.
+Важно! 
+•   Вне зависимости от схемы работы с КА по выдаче фреона списания должны производиться ежемесячно;
+•   Филиалы, где в настоящее время проходят пилоты: Саратов Восток, Каневская, Новороссийск Восток, Воронеж Север, Тольятти исключены из данной задачи;
+•   Совместно с ОЦО согласованы и внедрены правила списания фреона:
+1.  По торговым форматам списания с подразделения «Склад Экспл Армавир (Советской Армии 36)» возможно только на подразделения торговых объектов ММ (МД) и БФ. Наименование Склада указано в качестве примера;
+2.  Списание фреона по форматам БФ необходимо производить на подразделения с типовым наименованием «Торговый зал Волгоград 1 Генерала Штеменко». Объект Волгоград 1 Генерала Штеменко указан в качестве примера. Списания на типовые подразделения «Инженерный» или «Сектора торговли» запрещаются;
+3.  Списание фреона по РЦ с подразделения «Экспл ГИ РЦ Астрахань» возможно только на подразделение «Склад РЦ Астрахань».
+•   Перемещение по учёту фреона со складов хранения фреона на другие склады или ТТ (внутри филиала или РЦ) запрещается, кроме ситуаций при закрытии склада и кодировки нового.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,52 +513,6 @@
 1. В кабинете №7 (ОИТ) необходимо выполнить герметизацию примыканий окон к стенам. Промерзание в местах примыкания в ОЗП.
 2. В кабинете № 13 на радиатор смонтировать боковой автоматический воздухоотводчик.
 3. В кабинете ДФ МК смонтировать на радиатор боковой автоматический воздухоотводчик.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Владикавказ</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46319</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SMT-в00011341893</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Инженерный отдел Владикавказ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ежемесячное списание фреона_сентябрь_2026 Добрый день!
-Коллеги, ввиду наличия системной проблемы со списанием фреона с октября 2025 года на ежемесячной основе будет выполняться постановка задачи по списанию на все филиалы и РЦ.
-Срок выполнения задачи с 10 по 20 число каждого месяца. Централизованная поставка фреона на филиалы и РЦ будет учитывать текущие остатки по БУ, ввиду чего фактические остатки должны соответствовать остаткам БУ.
-Для выполнения задачи всем филиалам и РЦ требуется:
-1.  Выполнить списание фреона за последний отчётный период (месяц). Объем списания рассчитывается исходя из норматива расхода:
-•   ММ – 0,058 баллонов в месяц;
-•   БФ – 1,7 баллонов в месяц;
-•   РЦ – 10 баллонов в месяц.
-2.  При закрытии задачи в комментариях указать номер заявки в СЭД на списание.
-Важно! 
-•   Вне зависимости от схемы работы с КА по выдаче фреона списания должны производиться ежемесячно;
-•   Филиалы, где в настоящее время проходят пилоты: Саратов Восток, Каневская, Новороссийск Восток, Воронеж Север, Тольятти исключены из данной задачи;
-•   Совместно с ОЦО согласованы и внедрены правила списания фреона:
-1.  По торговым форматам списания с подразделения «Склад Экспл Армавир (Советской Армии 36)» возможно только на подразделения торговых объектов ММ (МД) и БФ. Наименование Склада указано в качестве примера;
-2.  Списание фреона по форматам БФ необходимо производить на подразделения с типовым наименованием «Торговый зал Волгоград 1 Генерала Штеменко». Объект Волгоград 1 Генерала Штеменко указан в качестве примера. Списания на типовые подразделения «Инженерный» или «Сектора торговли» запрещаются;
-3.  Списание фреона по РЦ с подразделения «Экспл ГИ РЦ Астрахань» возможно только на подразделение «Склад РЦ Астрахань».
-•   Перемещение по учёту фреона со складов хранения фреона на другие склады или ТТ (внутри филиала или РЦ) запрещается, кроме ситуаций при закрытии склада и кодировки нового.</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,39 +480,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Пенза</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46306.59444444445</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SMT-в00011245542</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Администрация Пенза</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Офис Пензенского филиала АО Тандер.
-1. В кабинете №7 (ОИТ) необходимо выполнить герметизацию примыканий окон к стенам. Промерзание в местах примыкания в ОЗП.
-2. В кабинете № 13 на радиатор смонтировать боковой автоматический воздухоотводчик.
-3. В кабинете ДФ МК смонтировать на радиатор боковой автоматический воздухоотводчик.</t>
         </is>
       </c>
     </row>
